--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488162_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488162_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. LLANO ABASCAL</t>
+          <t>F. COTAN MOYA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2737</v>
+        <v>4.4148</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4832</v>
+        <v>4.6733</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2095</v>
+        <v>-0.2585</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2074</v>
+        <v>2.5216</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1058</v>
+        <v>2.7617</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8984</v>
+        <v>-0.2402</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0879</v>
+        <v>4.7681</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2585</v>
+        <v>2.2974</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8294</v>
+        <v>2.4707</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8804999999999999</v>
+        <v>-2.2465</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.4643</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.7278</v>
+        <v>-2.7108</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.8529</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4823</v>
+        <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2096</v>
+        <v>0.6065</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3217</v>
+        <v>-0.0948</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8879</v>
+        <v>0.7013</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.6992</v>
+        <v>-0.5662</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.6992</v>
+        <v>-0.5662</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9225</v>
+        <v>4.021</v>
       </c>
       <c r="E3" t="n">
         <v>5.155</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2325</v>
+        <v>-1.134</v>
       </c>
       <c r="G3" t="n">
         <v>0.8809</v>
@@ -688,13 +688,13 @@
         <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7397</v>
+        <v>0.8381</v>
       </c>
       <c r="T3" t="n">
         <v>0.0684</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6712</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>4.1548</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. COTAN MOYA</t>
+          <t>A. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7035</v>
+        <v>2.953</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1837</v>
+        <v>2.9164</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4801</v>
+        <v>0.0367</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5216</v>
+        <v>2.2074</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7617</v>
+        <v>3.1058</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2402</v>
+        <v>-0.8984</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7681</v>
+        <v>3.0879</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2974</v>
+        <v>2.2585</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4707</v>
+        <v>0.8294</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2465</v>
+        <v>-0.8804999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4643</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.7108</v>
+        <v>-1.7278</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8529</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8529</v>
+        <v>1.4823</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1047</v>
+        <v>1.8889</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5844</v>
+        <v>0.7549</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4797</v>
+        <v>1.1341</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5662</v>
+        <v>-1.6992</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5662</v>
+        <v>-1.6992</v>
       </c>
     </row>
     <row r="5">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.5878</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6261</v>
+        <v>0.3324</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3047</v>
+        <v>0.2555</v>
       </c>
       <c r="G6" t="n">
         <v>0.6496</v>
@@ -922,13 +922,13 @@
         <v>0.1853</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3925</v>
+        <v>0.0494</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5434</v>
+        <v>0.2496</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.151</v>
+        <v>-0.2002</v>
       </c>
       <c r="V6" t="n">
         <v>0.63</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3096</v>
+        <v>-0.5542</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.627</v>
+        <v>-0.9208</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3174</v>
+        <v>0.3667</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1047</v>
@@ -1000,13 +1000,13 @@
         <v>0.3706</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4245</v>
+        <v>0.18</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5099</v>
+        <v>0.2161</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0853</v>
+        <v>-0.0361</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3087</v>
+        <v>-1.26</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0853</v>
+        <v>-0.9873</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2234</v>
+        <v>-0.2727</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7055</v>
@@ -1078,13 +1078,13 @@
         <v>1.4823</v>
       </c>
       <c r="S8" t="n">
-        <v>0.666</v>
+        <v>0.7147</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1269</v>
+        <v>0.2248</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5392</v>
+        <v>0.4899</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8251</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4925</v>
+        <v>-1.5955</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6209</v>
+        <v>-0.8375</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1284</v>
+        <v>-0.758</v>
       </c>
       <c r="G9" t="n">
         <v>-2.095</v>
@@ -1156,13 +1156,13 @@
         <v>2.0382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.966</v>
+        <v>0.863</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9426</v>
+        <v>-0.1591</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9085</v>
+        <v>1.0222</v>
       </c>
       <c r="V9" t="n">
         <v>0.3777</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7115</v>
+        <v>-3.3439</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2909</v>
+        <v>-1.9971</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4206</v>
+        <v>-1.3467</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3346</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.136</v>
+        <v>0.2316</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2189</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0828</v>
+        <v>0.1567</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3144</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9421</v>
+        <v>-3.9667</v>
       </c>
       <c r="E11" t="n">
         <v>-3.2567</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6854</v>
+        <v>-0.71</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1845</v>
@@ -1312,13 +1312,13 @@
         <v>0.3706</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7247</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="T11" t="n">
         <v>0.4004</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3243</v>
+        <v>0.2997</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.974</v>
+        <v>-7.1643</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.307</v>
+        <v>-3.8174</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.667</v>
+        <v>-3.3469</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0891</v>
@@ -1390,13 +1390,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9443</v>
+        <v>-0.1346</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7449</v>
+        <v>-0.2552</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1995</v>
+        <v>0.1206</v>
       </c>
       <c r="V12" t="n">
         <v>-2.6436</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.697500000000002</v>
+        <v>-3.697699999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>3.470500000000001</v>
+        <v>3.4706</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.167999999999999</v>
+        <v>-7.167899999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-4.043600000000001</v>
@@ -1468,13 +1468,13 @@
         <v>10.191</v>
       </c>
       <c r="S13" t="n">
-        <v>5.938</v>
+        <v>5.9377</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4799</v>
+        <v>1.48</v>
       </c>
       <c r="U13" t="n">
-        <v>4.457800000000001</v>
+        <v>4.4579</v>
       </c>
       <c r="V13" t="n">
         <v>-1.886000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9454</v>
+        <v>3.5382</v>
       </c>
       <c r="E14" t="n">
-        <v>3.452</v>
+        <v>2.7665</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4934</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>4.8433</v>
@@ -1546,13 +1546,13 @@
         <v>1.297</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0445</v>
+        <v>-0.4517</v>
       </c>
       <c r="T14" t="n">
-        <v>0.342</v>
+        <v>-0.3435</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3865</v>
+        <v>-0.1082</v>
       </c>
       <c r="V14" t="n">
         <v>0.6289</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2897</v>
+        <v>3.2725</v>
       </c>
       <c r="E15" t="n">
         <v>4.1992</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9095</v>
+        <v>-0.9267</v>
       </c>
       <c r="G15" t="n">
         <v>1.841</v>
@@ -1624,13 +1624,13 @@
         <v>2.594</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8483000000000001</v>
+        <v>-0.8655</v>
       </c>
       <c r="T15" t="n">
         <v>-0.8244</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0239</v>
+        <v>-0.0411</v>
       </c>
       <c r="V15" t="n">
         <v>0.6294</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2824</v>
+        <v>2.8865</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6482</v>
+        <v>2.942</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3658</v>
+        <v>-0.0554</v>
       </c>
       <c r="G16" t="n">
         <v>1.5691</v>
@@ -1702,13 +1702,13 @@
         <v>1.297</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2306</v>
+        <v>-0.6264</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1826</v>
+        <v>-0.8888</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.048</v>
+        <v>0.2624</v>
       </c>
       <c r="V16" t="n">
         <v>1.5733</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.999</v>
+        <v>1.7624</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6138</v>
+        <v>1.2221</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3851</v>
+        <v>0.5403</v>
       </c>
       <c r="G17" t="n">
         <v>1.4603</v>
@@ -1780,13 +1780,13 @@
         <v>0.3706</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1681</v>
+        <v>-0.0684</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2699</v>
+        <v>-0.1219</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1017</v>
+        <v>0.0535</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. LÓPEZ CALZADA</t>
+          <t>L. DALLACOSTA ORTIZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6221</v>
+        <v>0.766</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6221</v>
+        <v>0.1251</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.6409</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6221</v>
+        <v>-0.679</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-1.0399</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6221</v>
+        <v>0.3609</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6221</v>
+        <v>0.339</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.1932</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6221</v>
+        <v>0.1458</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-1.018</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-1.2331</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.2152</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.8529</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.1104</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. DALLACOSTA ORTIZ</t>
+          <t>L. LÓPEZ CALZADA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5364</v>
+        <v>0.6221</v>
       </c>
       <c r="E19" t="n">
-        <v>0.223</v>
+        <v>0.6221</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3134</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.679</v>
+        <v>0.6221</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0399</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3609</v>
+        <v>0.6221</v>
       </c>
       <c r="J19" t="n">
-        <v>0.339</v>
+        <v>0.6221</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1932</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1458</v>
+        <v>0.6221</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.018</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2331</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2152</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1816</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5215</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.017</v>
+        <v>0.1371</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0244</v>
+        <v>0.1715</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0074</v>
+        <v>-0.0344</v>
       </c>
       <c r="G21" t="n">
         <v>0.7338</v>
@@ -2092,13 +2092,13 @@
         <v>0.7411</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.233</v>
+        <v>-0.079</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.143</v>
+        <v>0.0529</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.09</v>
+        <v>-0.1318</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2589</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0634</v>
+        <v>-1.1619</v>
       </c>
       <c r="E22" t="n">
         <v>-0.3283</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7351</v>
+        <v>-0.8336</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9977</v>
@@ -2170,13 +2170,13 @@
         <v>0.1853</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2509</v>
+        <v>-0.3494</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3283</v>
       </c>
       <c r="U22" t="n">
-        <v>0.07729999999999999</v>
+        <v>-0.0211</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5525</v>
+        <v>-1.3561</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4816</v>
+        <v>-1.3837</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0709</v>
+        <v>0.0276</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3235</v>
@@ -2248,13 +2248,13 @@
         <v>0.1853</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4143</v>
+        <v>-0.2179</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2189</v>
+        <v>-0.1209</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1955</v>
+        <v>-0.097</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8785</v>
+        <v>-2.7239</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3216</v>
+        <v>-1.2237</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5569</v>
+        <v>-1.5002</v>
       </c>
       <c r="G24" t="n">
         <v>-0.8981</v>
@@ -2326,13 +2326,13 @@
         <v>2.7793</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.018</v>
+        <v>-0.8633</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9127</v>
+        <v>-0.8148</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1052</v>
+        <v>-0.0485</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8888</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.788</v>
+        <v>-3.0619</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.7564</v>
+        <v>-2.2668</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0316</v>
+        <v>-0.7951</v>
       </c>
       <c r="G25" t="n">
         <v>-3.4497</v>
@@ -2404,13 +2404,13 @@
         <v>2.594</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7263</v>
+        <v>-1.0001</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.6414</v>
+        <v>-1.1518</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0848</v>
+        <v>0.1517</v>
       </c>
       <c r="V25" t="n">
         <v>1.5733</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3.697699999999999</v>
+        <v>5.0031</v>
       </c>
       <c r="E26" t="n">
-        <v>7.168099999999998</v>
+        <v>7.168099999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.4705</v>
+        <v>-2.1649</v>
       </c>
       <c r="G26" t="n">
         <v>4.0437</v>
@@ -2482,13 +2482,13 @@
         <v>13.8965</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.9378</v>
+        <v>-4.6321</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.457800000000001</v>
+        <v>-4.4579</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.4798</v>
+        <v>-0.1741</v>
       </c>
       <c r="V26" t="n">
         <v>1.8861</v>
